--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487430_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487430_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7845</v>
+        <v>9.1938</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8483</v>
+        <v>7.2577</v>
       </c>
       <c r="F2" t="n">
         <v>1.9362</v>
@@ -610,10 +610,10 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7834</v>
+        <v>-0.3741</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1704</v>
+        <v>-0.7611</v>
       </c>
       <c r="U2" t="n">
         <v>0.387</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5072</v>
+        <v>5.5561</v>
       </c>
       <c r="E3" t="n">
-        <v>1.786</v>
+        <v>1.8883</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7213</v>
+        <v>3.6678</v>
       </c>
       <c r="G3" t="n">
         <v>3.6146</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0533</v>
+        <v>-0.0044</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8734</v>
+        <v>-0.7711</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>3.3169</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3529</v>
+        <v>2.2076</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1495</v>
+        <v>1.0043</v>
       </c>
       <c r="F4" t="n">
         <v>1.2033</v>
@@ -766,10 +766,10 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2345</v>
+        <v>1.0892</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7111</v>
+        <v>0.5658</v>
       </c>
       <c r="U4" t="n">
         <v>0.5234</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2952</v>
+        <v>1.2569</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4507</v>
+        <v>2.3054</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1554</v>
+        <v>-1.0485</v>
       </c>
       <c r="G5" t="n">
         <v>3.9508</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5818</v>
+        <v>0.5434</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5634</v>
+        <v>0.4182</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0184</v>
+        <v>0.1253</v>
       </c>
       <c r="V5" t="n">
         <v>-3.0415</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7013</v>
+        <v>0.7768</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6862</v>
+        <v>0.0203</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3876</v>
+        <v>0.7565</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4307</v>
+        <v>-0.3064</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5976</v>
+        <v>1.068</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1669</v>
+        <v>-1.3745</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8932</v>
+        <v>0.0258</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0549</v>
+        <v>1.9513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1617</v>
+        <v>-1.9255</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5375</v>
+        <v>-0.3323</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5427</v>
+        <v>-0.8833</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0052</v>
+        <v>0.551</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4869</v>
+        <v>0.4968</v>
       </c>
       <c r="T6" t="n">
-        <v>0.207</v>
+        <v>-0.0471</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2799</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6659</v>
+        <v>0.3905</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6659</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6952</v>
+        <v>0.6165</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1414</v>
+        <v>-0.5839</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8367</v>
+        <v>1.2004</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3064</v>
+        <v>-1.4307</v>
       </c>
       <c r="H7" t="n">
-        <v>1.068</v>
+        <v>-1.5976</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3745</v>
+        <v>0.1669</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0258</v>
+        <v>-0.8932</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9513</v>
+        <v>-1.0549</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9255</v>
+        <v>0.1617</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3323</v>
+        <v>-0.5375</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8833</v>
+        <v>-0.5427</v>
       </c>
       <c r="O7" t="n">
-        <v>0.551</v>
+        <v>0.0052</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4153</v>
+        <v>0.4021</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2088</v>
+        <v>0.3094</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6241</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3905</v>
+        <v>0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0451</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0477</v>
+        <v>-0.8431</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9851</v>
+        <v>0.798</v>
       </c>
       <c r="G8" t="n">
         <v>0.2502</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005</v>
+        <v>0.0181</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.22</v>
+        <v>-0.0153</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2205</v>
+        <v>0.0334</v>
       </c>
       <c r="V8" t="n">
         <v>0.6659</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4183</v>
+        <v>-0.8084</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1749</v>
+        <v>1.81</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2434</v>
+        <v>-2.6184</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6432</v>
+        <v>1.0433</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3151</v>
+        <v>-2.0286</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6719000000000001</v>
+        <v>3.0719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9714</v>
+        <v>2.0443</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6536</v>
+        <v>-0.4662</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>2.5106</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3281</v>
+        <v>-1.001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3385</v>
+        <v>-1.5624</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0104</v>
+        <v>0.5614</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8014</v>
+        <v>-0.4346</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0081</v>
+        <v>-0.4717</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2067</v>
+        <v>0.0371</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.492</v>
+        <v>-2.9839</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.492</v>
+        <v>-4.2005</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6881</v>
+        <v>-1.6568</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1921</v>
+        <v>-2.2944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.504</v>
+        <v>0.6377</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6123</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0538</v>
+        <v>-0.0225</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0129</v>
+        <v>-0.1153</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0409</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0.3905</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.798</v>
+        <v>-2.0844</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0343</v>
+        <v>-0.6272</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8323</v>
+        <v>-1.4572</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0433</v>
+        <v>0.6432</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0286</v>
+        <v>1.3151</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0719</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0443</v>
+        <v>0.9714</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4662</v>
+        <v>1.6536</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5106</v>
+        <v>-0.6822</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.001</v>
+        <v>-0.3281</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5624</v>
+        <v>-0.3385</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5614</v>
+        <v>0.0104</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5668</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R11" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4242</v>
+        <v>0.1353</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2474</v>
+        <v>0.5558</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1768</v>
+        <v>-0.4205</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9839</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.2005</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4684</v>
+        <v>-3.8151</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2319</v>
+        <v>-3.8459</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2365</v>
+        <v>0.0309</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3179</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7528</v>
+        <v>0.4061</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7287</v>
+        <v>0.1147</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0241</v>
+        <v>0.2914</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4908</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.9008</v>
+        <v>11.1979</v>
       </c>
       <c r="E13" t="n">
-        <v>5.794600000000001</v>
+        <v>6.0915</v>
       </c>
       <c r="F13" t="n">
-        <v>5.106599999999999</v>
+        <v>5.106699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>10.7549</v>
@@ -1450,16 +1450,16 @@
         <v>8.609499999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.286499999999999</v>
+        <v>-4.2865</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.483700000000001</v>
+        <v>-8.483699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1975</v>
+        <v>4.197500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.6263</v>
@@ -1468,13 +1468,13 @@
         <v>17.6261</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9585</v>
+        <v>2.2554</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5146000000000001</v>
+        <v>-0.2177</v>
       </c>
       <c r="U13" t="n">
-        <v>2.473099999999999</v>
+        <v>2.4732</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8123</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4243</v>
+        <v>2.2629</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2428</v>
+        <v>0.7311</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1815</v>
+        <v>1.5318</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6731</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4684</v>
+        <v>0.307</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8475</v>
+        <v>0.3358</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3791</v>
+        <v>-0.0288</v>
       </c>
       <c r="V14" t="n">
         <v>2.4332</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0975</v>
+        <v>1.2835</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7094</v>
+        <v>1.0316</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6119</v>
+        <v>0.2519</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1192</v>
+        <v>1.4635</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8415</v>
+        <v>0.261</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9607</v>
+        <v>1.2024</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1485</v>
+        <v>0.774</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5842</v>
+        <v>0.1225</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4357</v>
+        <v>0.6515</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2677</v>
+        <v>0.6895</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7427</v>
+        <v>0.1385</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.525</v>
+        <v>0.551</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.1336</v>
+        <v>0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.0921</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7004</v>
+        <v>0.3327</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2358</v>
+        <v>0.2576</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4646</v>
+        <v>0.0751</v>
       </c>
       <c r="V15" t="n">
-        <v>3.6498</v>
+        <v>-1.492</v>
       </c>
       <c r="W15" t="n">
-        <v>5.4171</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7673</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7497</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4175</v>
+        <v>2.8009</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3321</v>
+        <v>-2.2117</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4635</v>
+        <v>2.886</v>
       </c>
       <c r="H16" t="n">
-        <v>0.261</v>
+        <v>2.1178</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2024</v>
+        <v>0.7683</v>
       </c>
       <c r="J16" t="n">
-        <v>0.774</v>
+        <v>3.886</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1225</v>
+        <v>2.5927</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6515</v>
+        <v>1.2933</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6895</v>
+        <v>-1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1385</v>
+        <v>-0.475</v>
       </c>
       <c r="O16" t="n">
-        <v>0.551</v>
+        <v>-0.525</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R16" t="n">
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2011</v>
+        <v>0.3323</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3564</v>
+        <v>0.1476</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1553</v>
+        <v>0.1847</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.492</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.2831</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8009</v>
+        <v>0.9931</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2117</v>
+        <v>-0.71</v>
       </c>
       <c r="G17" t="n">
-        <v>2.886</v>
+        <v>-0.1192</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1178</v>
+        <v>1.8415</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7683</v>
+        <v>-1.9607</v>
       </c>
       <c r="J17" t="n">
-        <v>3.886</v>
+        <v>1.1485</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5927</v>
+        <v>2.5842</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2933</v>
+        <v>-1.4357</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>-1.2677</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.475</v>
+        <v>-0.7427</v>
       </c>
       <c r="O17" t="n">
         <v>-0.525</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1958</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1751</v>
+        <v>-5.0921</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3323</v>
+        <v>-0.114</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1476</v>
+        <v>-0.4805</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1847</v>
+        <v>0.3666</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4332</v>
+        <v>3.6498</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0576</v>
+        <v>5.4171</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3756</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7863</v>
+        <v>-0.7881</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2808</v>
+        <v>-0.1784</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5056</v>
+        <v>-0.6097</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8546</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0528</v>
+        <v>-0.0545</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9922</v>
+        <v>-0.8899</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9394</v>
+        <v>0.8353</v>
       </c>
       <c r="V18" t="n">
         <v>2.1003</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1574</v>
+        <v>-1.0539</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1355</v>
+        <v>-0.6731</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9781</v>
+        <v>-0.3809</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9079</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7866</v>
+        <v>0.8068</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1212</v>
+        <v>-1.5513</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4381</v>
+        <v>1.1242</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5189</v>
+        <v>1.3474</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0808</v>
+        <v>-0.2232</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4698</v>
+        <v>-1.8687</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2677</v>
+        <v>-0.5406</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2021</v>
+        <v>-1.3281</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.1942</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1317</v>
+        <v>-0.507</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6484</v>
+        <v>0.3127</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9412</v>
+        <v>-0.1152</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3905</v>
+        <v>-0.1152</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5241</v>
+        <v>-1.751</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9801</v>
+        <v>-2.5448</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5441</v>
+        <v>0.7938</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-1.9079</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8068</v>
+        <v>-0.7866</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5513</v>
+        <v>-1.1212</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1242</v>
+        <v>-0.4381</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3474</v>
+        <v>-0.5189</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2232</v>
+        <v>0.0808</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8687</v>
+        <v>-1.4698</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5406</v>
+        <v>-0.2677</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3281</v>
+        <v>-1.2021</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6644</v>
+        <v>-0.077</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.5411</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1496</v>
+        <v>0.464</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1152</v>
+        <v>-0.9412</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1152</v>
+        <v>-0.3905</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3866</v>
+        <v>-2.2797</v>
       </c>
       <c r="E21" t="n">
         <v>-0.205</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1816</v>
+        <v>-2.0747</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0801</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3445</v>
+        <v>-0.2376</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4158</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0713</v>
+        <v>0.1782</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5495</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0233</v>
+        <v>-3.6247</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.481</v>
+        <v>-4.4193</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5423</v>
+        <v>0.7946</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5504</v>
+        <v>-3.475</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3379</v>
+        <v>0.2439</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2125</v>
+        <v>-3.7189</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7286</v>
+        <v>-2.0698</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0464</v>
+        <v>1.2605</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6822</v>
+        <v>-3.3304</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8218</v>
+        <v>-1.4052</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2916</v>
+        <v>-1.0166</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5302</v>
+        <v>-0.3886</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5875</v>
+        <v>0.5875</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5668</v>
+        <v>2.7419</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1607</v>
+        <v>-0.6221</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0708</v>
+        <v>-0.5421</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2754</v>
+        <v>-0.1152</v>
       </c>
       <c r="W22" t="n">
-        <v>1.492</v>
+        <v>-0.1152</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2258</v>
+        <v>-4.3571</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7263</v>
+        <v>-2.788</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5006</v>
+        <v>-1.5691</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.475</v>
+        <v>-3.5504</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2439</v>
+        <v>-2.3379</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7189</v>
+        <v>-1.2125</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0698</v>
+        <v>-1.7286</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2605</v>
+        <v>-1.0464</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.3304</v>
+        <v>-0.6822</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4052</v>
+        <v>-1.8218</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0166</v>
+        <v>-1.2916</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3886</v>
+        <v>-0.5302</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5875</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2231</v>
+        <v>-0.4945</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.387</v>
+        <v>-0.397</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8361</v>
+        <v>-0.0975</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1152</v>
+        <v>0.2754</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1152</v>
+        <v>1.492</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.242799999999999</v>
+        <v>-9.4358</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6381</v>
+        <v>-5.251899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.604899999999999</v>
+        <v>-4.184</v>
       </c>
       <c r="G24" t="n">
-        <v>-9.055300000000001</v>
+        <v>-9.055299999999999</v>
       </c>
       <c r="H24" t="n">
         <v>2.7718</v>
@@ -2299,10 +2299,10 @@
         <v>-11.8271</v>
       </c>
       <c r="J24" t="n">
-        <v>4.042500000000001</v>
+        <v>4.0425</v>
       </c>
       <c r="K24" t="n">
-        <v>8.320400000000001</v>
+        <v>8.320399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-4.2781</v>
@@ -2311,10 +2311,10 @@
         <v>-13.0978</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.5487</v>
+        <v>-5.548699999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.548999999999999</v>
+        <v>-7.549</v>
       </c>
       <c r="P24" t="n">
         <v>-1.371</v>
@@ -2326,16 +2326,16 @@
         <v>16.0595</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6289</v>
+        <v>-0.8219000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9562</v>
+        <v>-2.5703</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3273</v>
+        <v>1.7482</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8124</v>
+        <v>1.812399999999999</v>
       </c>
       <c r="W24" t="n">
         <v>10.7065</v>
